--- a/workshop-template.xlsx
+++ b/workshop-template.xlsx
@@ -2766,7 +2766,7 @@
       </c>
       <c r="C2" s="14" t="inlineStr">
         <is>
-          <t>1.0 - 1.5 秒</t>
+          <t>0.9 - 1.9 秒</t>
         </is>
       </c>
       <c r="D2" s="14" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>2-3 个快切镜，配重音效（唰/咚），解说不停顿、不留气口</t>
+          <t>2-3 个快切镜，配重音效（唰/咚）；别再切到 0.8 秒/镜——TTS 和真人都读得发赶</t>
         </is>
       </c>
     </row>

--- a/workshop-template.xlsx
+++ b/workshop-template.xlsx
@@ -11,9 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="剪辑底稿" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="完整样例" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节奏规范" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材来源与检索词" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材台账" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材仓库索引" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材采集单" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材来源与检索词" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材台账" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材仓库索引" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'剪辑底稿'!$A$1:$L$31</definedName>
@@ -177,6 +178,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,12 +192,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -617,7 +618,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>① 剪辑底稿＝空白模板（照着填）　② 完整样例＝一份填好的 71 秒案例（照着学）　③ 节奏规范＝时长/语速硬标准　④ 素材来源与检索词＝素材去哪下、用什么词搜　⑤ 素材仓库索引＝素材怎么建库　⑥ 素材台账＝授权自保证据（每下一条记一行）</t>
+          <t>① 剪辑底稿＝空白模板（照着填）　② 完整样例＝一份填好的 71 秒案例（照着学）　③ 节奏规范＝时长/语速硬标准　④ 素材采集单＝这一期要办什么、找完打勾（照着办）　⑤ 素材来源与检索词＝素材去哪下、用什么词搜（参考）　⑥ 素材仓库索引＝素材怎么建库　⑦ 素材台账＝授权自保证据（每下一条记一行）</t>
         </is>
       </c>
     </row>
@@ -2989,6 +2990,241 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>覆盖镜次</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
+          <t>怎么做（检索词 / 拍摄内容）</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>去哪找</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
+          <t>要几条</t>
+        </is>
+      </c>
+      <c r="I1" s="6" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="11" t="inlineStr"/>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="11" t="inlineStr">
+        <is>
+          <t>L1 自拍</t>
+        </is>
+      </c>
+      <c r="D2" s="20" t="inlineStr">
+        <is>
+          <t>片头钩子 · 自拍空镜</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>001-002</t>
+        </is>
+      </c>
+      <c r="F2" s="20" t="inlineStr">
+        <is>
+          <t>手机拍：园区大门 / 拉闸门 / 车间过道横移 / 账本红字，每条 5-8 秒</t>
+        </is>
+      </c>
+      <c r="G2" s="20" t="inlineStr">
+        <is>
+          <t>自己拍（手机横屏）</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I2" s="20" t="inlineStr">
+        <is>
+          <t>这 3 秒决定完播。素材站的画面「没有你的厂味」，钩子必用自拍</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="14" t="inlineStr"/>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>厂房外景</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>005、009、013…</t>
+        </is>
+      </c>
+      <c r="F3" s="16" t="inlineStr">
+        <is>
+          <t>abandoned warehouse / factory closed / shutter door</t>
+        </is>
+      </c>
+      <c r="G3" s="16" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I3" s="16" t="inlineStr">
+        <is>
+          <t>本片复用 N 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="11" t="inlineStr"/>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>L1 自制</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>数据图表 · Excel 出图（叠加层）</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>005、007、032</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>用国家统计局 / 地方统计局 / 海关总署的官方数据，自己用 Excel 出图</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>自己做（Excel 截图或导出 PNG 透明底）</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="I4" s="20" t="inlineStr">
+        <is>
+          <t>这是叠加在场景素材上的透明图，不占镜次、不替代空镜。带数字的镜头一律上自己出的图</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>用法：从左往右办——『去哪找』决定你打开哪个站还是拿手机；办完一行就在「✓」列打个勾。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>浅蓝底 = 要你自己拍 / 自己出图（L1），先办这些；素材站的 L2 可以一次下满 30-50 条再动剪。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>底稿「画面素材」列永远留空——机器给场景建议和检索词，实际用哪个文件由你挑。这就是标准化的分界线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>下载后按「问题类型_场景_序号.mp4」命名，并记入「素材台账」（授权自保证据，必须记）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A7:I7"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="A6:I6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3027,7 +3263,7 @@
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="20" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>L1 自拍空镜</t>
         </is>
@@ -3054,7 +3290,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>L2 免费站</t>
         </is>
@@ -3081,7 +3317,7 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>L2 免费站</t>
         </is>
@@ -3108,7 +3344,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>L2 免费站</t>
         </is>
@@ -3135,7 +3371,7 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="22" t="inlineStr">
         <is>
           <t>L2 免费站</t>
         </is>
@@ -3162,7 +3398,7 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="22" t="inlineStr">
         <is>
           <t>L2 免费站</t>
         </is>
@@ -3189,7 +3425,7 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="22" t="inlineStr">
         <is>
           <t>L3 AI 生成</t>
         </is>
@@ -3216,7 +3452,7 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>L3 AI 生成</t>
         </is>
@@ -3243,7 +3479,7 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>L4 付费订阅</t>
         </is>
@@ -3270,7 +3506,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="22" t="inlineStr">
         <is>
           <t>🚫 红线</t>
         </is>
@@ -3297,7 +3533,7 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="22" t="inlineStr">
         <is>
           <t>合规</t>
         </is>
@@ -3324,7 +3560,7 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="22" t="inlineStr">
         <is>
           <t>专业感</t>
         </is>
@@ -3351,7 +3587,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="23" t="inlineStr">
         <is>
           <t>检索词速查（主用英文，Pexels/Pixabay 英文命中率远高于中文）</t>
         </is>
@@ -3385,7 +3621,7 @@
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="22" t="inlineStr">
         <is>
           <t>倒闭关停</t>
         </is>
@@ -3412,7 +3648,7 @@
       </c>
     </row>
     <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
         <is>
           <t>亏损</t>
         </is>
@@ -3439,7 +3675,7 @@
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
         <is>
           <t>订单流失</t>
         </is>
@@ -3466,7 +3702,7 @@
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="22" t="inlineStr">
         <is>
           <t>转型失败</t>
         </is>
@@ -3493,7 +3729,7 @@
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
         <is>
           <t>质量事故</t>
         </is>
@@ -3520,7 +3756,7 @@
       </c>
     </row>
     <row r="22" ht="34" customHeight="1">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="22" t="inlineStr">
         <is>
           <t>欠款劳资</t>
         </is>
@@ -3547,7 +3783,7 @@
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>库存积压</t>
         </is>
@@ -3574,7 +3810,7 @@
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="22" t="inlineStr">
         <is>
           <t>现金流断裂</t>
         </is>
@@ -3601,22 +3837,22 @@
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="A25" s="24" t="inlineStr">
         <is>
           <t>通用底材</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>factory aerial / production line / robotic arm / assembly worker / forklift / cardboard boxes / industrial machine closeup / warehouse aisle</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>工厂 流水线 机械臂 叉车 纸箱</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
         <is>
           <t>所有制造业选题都能复用</t>
         </is>
@@ -3628,49 +3864,49 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="21" t="inlineStr">
+      <c r="A27" s="23" t="inlineStr">
         <is>
           <t>六个真正的提效动作</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>1. 一次搜一批，别一镜一搜：按「问题类型_场景_序号.mp4」命名，一次下满 30-50 条再动剪。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>2. 顺着「相似推荐」滚雪球：找到一条合用的，顺着下面的同系列一路下，风格天然统一。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>3. 先攒 20 条通用底材：车间、流水线、货车、货架各来几条，后面 60% 的镜头直接复用，不用现找。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>4. 色调统一靠后期：素材来源杂、色调也杂，套一层统一 LUT/调色预设，比挑「同色系素材」快 10 倍。</t>
         </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>5. AI 只用在实拍拍不到的地方：其余别用（AI 视频细节仍有破绽，一眼假）。</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>6. 拿不准就自己拍 5 秒：手机拍一段车间过道横移，比查 10 分钟授权快得多。</t>
         </is>
@@ -3699,7 +3935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4196,35 +4432,35 @@
       </c>
     </row>
     <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>1. 账号一旦商业化，被别人追究版权时，你唯一的防线就是这份台账——证明素材来源合法、授权合规。</t>
         </is>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>2. 第 2 行的灰色字是示例格式，照着填即可，正式使用时可删。</t>
         </is>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="24" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>3. 「是否需署名」填「是」的（Videvo 部分素材、Dareful/Mazwai 的 CC BY），片尾必须自动带上署名文案。</t>
         </is>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="24" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>4. 授权类型只认三种写法：免署名·可商用 / 需署名·可商用 / 不可商用（不可商用的直接删掉别用）。</t>
         </is>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>5. 顺手记录「用于哪期」，素材复用时可快速回溯，避免同一素材在相邻两期重复出现。</t>
         </is>
@@ -4242,7 +4478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4316,7 +4552,7 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>倒闭关停</t>
         </is>
@@ -4350,7 +4586,7 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>亏损</t>
         </is>
@@ -4386,7 +4622,7 @@
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>订单流失</t>
         </is>
@@ -4422,7 +4658,7 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>转型失败</t>
         </is>
@@ -4458,7 +4694,7 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>质量事故</t>
         </is>
@@ -4492,7 +4728,7 @@
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>欠款劳资</t>
         </is>
@@ -4526,7 +4762,7 @@
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>库存积压</t>
         </is>
@@ -4562,7 +4798,7 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>现金流断裂</t>
         </is>
@@ -4603,28 +4839,28 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>1. 目录结构：素材库 / 问题类型 / 场景 / 文件；上表数字 = 该问题类型在该场景建议备好的镜头条数。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>2. 命名规范：问题类型_场景_序号.ext，例：订单流失_厂房外景_001.mp4（序号三位，便于排序与引用）。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>3. 开底稿的前提：每张解剖卡至少能从仓库配出 6-8 个可用镜头，配不出就先补拍/补生成。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>4. 一次归好长期复用——素材仓库是能持续出片的底层资产，也是对标账号周更 2 期的真正底气。</t>
         </is>
